--- a/samples/scalar_values_template.xlsx
+++ b/samples/scalar_values_template.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0.00;[Red]-$#,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="0.00000000000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,6 +125,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,10 +501,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
@@ -859,6 +869,57 @@
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>explicit fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Float bit fidelity</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>{{ numeric.float_value }}</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>exact pinned-reader float bits</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>15-digit financial Decimal</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>{{ numeric.financial_amount }}</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>numeric amount: 1234567890123.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Decimal display scale</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>{{ numeric.scaled_amount }}</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>12.50 via authored format</t>
         </is>
       </c>
     </row>
